--- a/data/trans_camb/P1435-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1435-Provincia-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,55</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,2</t>
+          <t>-5,32; 0,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,12</t>
+          <t>-5,1; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -1,49</t>
+          <t>-6,67; -1,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,2</t>
+          <t>-5,32; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,12</t>
+          <t>-5,1; 1,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -1,49</t>
+          <t>-6,67; -1,51</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-90,21%</t>
+          <t>-88,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-90,21%</t>
+          <t>-88,67%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 68,35</t>
+          <t>-90,3; 61,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 64,92</t>
+          <t>-84,67; 60,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,74; -59,0</t>
+          <t>-97,74; -48,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 68,35</t>
+          <t>-90,3; 61,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 64,92</t>
+          <t>-84,67; 60,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-98,74; -59,0</t>
+          <t>-97,74; -48,25</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,81</t>
+          <t>-10,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,81</t>
+          <t>-10,97</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -7,13</t>
+          <t>-14,93; -7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -12,99</t>
+          <t>-19,8; -13,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -6,75</t>
+          <t>-15,63; -7,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -7,13</t>
+          <t>-14,93; -7,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -12,99</t>
+          <t>-19,8; -13,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -6,75</t>
+          <t>-15,63; -7,58</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-63,55%</t>
+          <t>-64,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,55%</t>
+          <t>-64,52%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,05; -48,1</t>
+          <t>-76,52; -48,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-98,91; -89,23</t>
+          <t>-98,92; -89,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -43,11</t>
+          <t>-76,87; -47,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,05; -48,1</t>
+          <t>-76,52; -48,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-98,91; -89,23</t>
+          <t>-98,92; -89,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -43,11</t>
+          <t>-76,87; -47,55</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,68</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,96</t>
+          <t>-4,84; 0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,2</t>
+          <t>-5,7; 0,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,9</t>
+          <t>-4,44; 1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,96</t>
+          <t>-4,84; 0,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,2</t>
+          <t>-5,7; 0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,9</t>
+          <t>-4,44; 1,25</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,07%</t>
+          <t>-35,41%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,07%</t>
+          <t>-35,41%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 39,52</t>
+          <t>-76,62; 35,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,37; 11,87</t>
+          <t>-81,59; 16,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 32,56</t>
+          <t>-70,79; 44,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 39,52</t>
+          <t>-76,62; 35,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,37; 11,87</t>
+          <t>-81,59; 16,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 32,56</t>
+          <t>-70,79; 44,69</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>-2,91</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,61</t>
+          <t>-6,7; -0,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,38</t>
+          <t>-8,65; -3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 42,22</t>
+          <t>-6,18; 0,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,61</t>
+          <t>-6,7; -0,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,38</t>
+          <t>-8,65; -3,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 42,22</t>
+          <t>-6,18; 0,72</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146,58%</t>
+          <t>-40,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>146,58%</t>
+          <t>-40,83%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-76,03; -7,74</t>
+          <t>-75,19; 9,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-94,41; -56,31</t>
+          <t>-94,76; -59,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 680,4</t>
+          <t>-69,68; 17,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,03; -7,74</t>
+          <t>-75,19; 9,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-94,41; -56,31</t>
+          <t>-94,76; -59,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 680,4</t>
+          <t>-69,68; 17,82</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,29</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,99</t>
+          <t>1,31; 9,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,82</t>
+          <t>-4,31; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,61</t>
+          <t>2,57; 9,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,99</t>
+          <t>1,31; 9,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,82</t>
+          <t>-4,31; 1,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,61</t>
+          <t>2,57; 9,84</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229,9%</t>
+          <t>237,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>229,9%</t>
+          <t>237,03%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 873,13</t>
+          <t>12,0; 908,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 257,68</t>
+          <t>-92,81; 186,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,07; 856,1</t>
+          <t>37,23; 897,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 873,13</t>
+          <t>12,0; 908,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 257,68</t>
+          <t>-92,81; 186,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,07; 856,1</t>
+          <t>37,23; 897,18</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,92</t>
+          <t>-4,18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,92</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,86</t>
+          <t>-6,2; 3,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -5,36</t>
+          <t>-12,1; -5,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,31</t>
+          <t>-8,12; -0,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,86</t>
+          <t>-6,2; 3,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -5,36</t>
+          <t>-12,1; -5,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,31</t>
+          <t>-8,12; -0,4</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-45,73%</t>
+          <t>-48,71%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-45,73%</t>
+          <t>-48,71%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 47,31</t>
+          <t>-55,37; 52,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -77,77</t>
+          <t>-100,0; -74,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 8,65</t>
+          <t>-73,33; -4,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 47,31</t>
+          <t>-55,37; 52,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -77,77</t>
+          <t>-100,0; -74,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 8,65</t>
+          <t>-73,33; -4,15</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>10,52</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,06</t>
+          <t>-3,34; 1,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,13</t>
+          <t>-2,47; 1,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,89</t>
+          <t>7,28; 13,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,06</t>
+          <t>-3,34; 1,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,13</t>
+          <t>-2,47; 1,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,89</t>
+          <t>7,28; 13,53</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>137,68%</t>
+          <t>222,15%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>137,68%</t>
+          <t>222,15%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 30,35</t>
+          <t>-55,05; 35,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 59,23</t>
+          <t>-41,78; 59,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 268,42</t>
+          <t>115,09; 376,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 30,35</t>
+          <t>-55,05; 35,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 59,23</t>
+          <t>-41,78; 59,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 268,42</t>
+          <t>115,09; 376,3</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -4,18</t>
+          <t>-8,44; -4,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -4,79</t>
+          <t>-9,09; -5,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -3,9</t>
+          <t>-8,18; -3,87</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -4,18</t>
+          <t>-8,44; -4,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -4,79</t>
+          <t>-9,09; -5,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -3,9</t>
+          <t>-8,18; -3,87</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-73,88%</t>
+          <t>-73,86%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-73,88%</t>
+          <t>-73,86%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-89,18; -63,45</t>
+          <t>-89,86; -64,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-94,77; -75,69</t>
+          <t>-94,58; -75,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-85,53; -56,99</t>
+          <t>-85,36; -56,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-89,18; -63,45</t>
+          <t>-89,86; -64,4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-94,77; -75,69</t>
+          <t>-94,58; -75,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-85,53; -56,99</t>
+          <t>-85,36; -56,81</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
     </row>
@@ -1882,32 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
     </row>
@@ -1958,32 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
     </row>
